--- a/ESERCIZIO_M2-1-3_dati - Copia.xlsx
+++ b/ESERCIZIO_M2-1-3_dati - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3965ca6def52ccf6/Desktop/Epicode/Lavori/1° Settimana/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="11_5000B52A0906CB6F8FF94A95BF213A9D55C1F33E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EAD2DAD-720F-48E4-AB3D-20168AAC1030}"/>
+  <xr:revisionPtr revIDLastSave="408" documentId="11_5000B52A0906CB6F8FF94A95BF213A9D55C1F33E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EB55A6-650E-4D13-8810-2592ED53F933}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,16 +19,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Snacks!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Snacks!$D$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Snacks!$B$1</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Snacks!$B$2:$B$11</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Snacks!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Snacks!$C$1</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Snacks!$C$2:$C$11</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Snacks!$D$2:$D$11</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Snacks!$B$1</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Snacks!$C$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Snacks!$C$2:$C$11</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Snacks!$B$2:$B$11</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">Snacks!$A$2:$A$11</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Snacks!$E$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Snacks!$E$2:$E$11</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Snacks!$D$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Snacks!$D$2:$D$11</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">Snacks!$A$2:$A$11</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">Snacks!$E$1</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">Snacks!$E$2:$E$11</definedName>
@@ -229,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -240,55 +237,82 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="5" tint="-0.249977111117893"/>
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color theme="5" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color theme="7" tint="-0.499984740745262"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -298,32 +322,44 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -340,6 +376,222 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Book Antiqua"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -445,72 +697,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border outline="0">
-        <left style="thin">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color theme="7" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </left>
-        <right style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </right>
-        <top style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </top>
-        <bottom style="medium">
-          <color theme="5" tint="-0.249977111117893"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -525,102 +711,6 @@
         <name val="Arial"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Book Antiqua"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -676,7 +766,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>VOTAZIONE</a:t>
+              <a:t>PREFERENZE</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
@@ -711,7 +801,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="it-IT"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -984,7 +1074,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -999,7 +1089,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1085,7 +1174,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -1100,7 +1189,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1186,7 +1274,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -1201,7 +1289,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1293,7 +1380,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1405,7 +1492,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1511,7 +1598,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -1617,7 +1704,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="it-IT"/>
+                  <a:endParaRPr lang="en-US"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -2270,6 +2357,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="80"/>
+          <c:min val="69"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3177,10 +3265,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.9</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3219,7 +3307,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{40025D2F-789E-45D3-925A-5DCBAB444F68}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:f>_xlchart.v1.1</cx:f>
               <cx:v>Italia</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3262,10 +3350,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.12</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.14</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3304,7 +3392,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{B10A8057-0277-4793-B1F4-915DDD6082B1}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.13</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Francia</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3352,10 +3440,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3394,7 +3482,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{BB121593-2718-4984-9CC4-B1BF7FEE81E1}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Germania</cx:v>
             </cx:txData>
           </cx:tx>
@@ -3442,10 +3530,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -3484,7 +3572,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{BBF2D9DA-800F-4703-9628-BE656B520586}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.7</cx:f>
               <cx:v>Spagna</cx:v>
             </cx:txData>
           </cx:tx>
@@ -7546,7 +7634,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="3870960" y="0"/>
-              <a:ext cx="2948940" cy="1817370"/>
+              <a:ext cx="2948940" cy="1550670"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7624,7 +7712,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="6819900" y="0"/>
-              <a:ext cx="2941320" cy="1821180"/>
+              <a:ext cx="2918460" cy="1554480"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7701,8 +7789,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3870960" y="1809750"/>
-              <a:ext cx="2964180" cy="1824990"/>
+              <a:off x="3870960" y="1543050"/>
+              <a:ext cx="2964180" cy="1764030"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7779,8 +7867,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6819900" y="1836420"/>
-              <a:ext cx="2956560" cy="1798320"/>
+              <a:off x="6819900" y="1569720"/>
+              <a:ext cx="2918460" cy="1737360"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7814,36 +7902,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88DA9C24-6D03-4014-86FE-D671584BDFD8}" name="Tabella1" displayName="Tabella1" ref="A1:B8" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88DA9C24-6D03-4014-86FE-D671584BDFD8}" name="Tabella1" displayName="Tabella1" ref="A1:B8" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:B8" xr:uid="{88DA9C24-6D03-4014-86FE-D671584BDFD8}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5FDE27F2-9560-4CEB-9718-93EA5A70532D}" name="CIBO" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{2F8566D4-3F49-41C4-9A47-AFA5E81CC256}" name="VOTI" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{5FDE27F2-9560-4CEB-9718-93EA5A70532D}" name="CIBO" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{2F8566D4-3F49-41C4-9A47-AFA5E81CC256}" name="VOTI" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28D2E3DD-C922-4459-AC41-476FCEB73E79}" name="Tabella2" displayName="Tabella2" ref="A1:B31" totalsRowShown="0" headerRowDxfId="11" dataDxfId="12" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{28D2E3DD-C922-4459-AC41-476FCEB73E79}" name="Tabella2" displayName="Tabella2" ref="A1:B31" totalsRowShown="0" headerRowDxfId="0" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
   <autoFilter ref="A1:B31" xr:uid="{28D2E3DD-C922-4459-AC41-476FCEB73E79}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A389577D-6C59-4C18-907F-5E446B480F0B}" name="GIORNO" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{602A1C1C-ACD4-47C0-9406-500A5B61DCC6}" name="PESO" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{A389577D-6C59-4C18-907F-5E446B480F0B}" name="GIORNO" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{602A1C1C-ACD4-47C0-9406-500A5B61DCC6}" name="PESO" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{572AEA4F-A44E-4AF1-B964-15834408DB3A}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{572AEA4F-A44E-4AF1-B964-15834408DB3A}" name="Tabella3" displayName="Tabella3" ref="A1:E11" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:E11" xr:uid="{572AEA4F-A44E-4AF1-B964-15834408DB3A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{57F8BC07-5C6C-4408-9160-2F0D9F6AFA18}" name="Snack" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{26F26539-D5D0-47BE-A212-86FC4674E49D}" name="Italia" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F6304A94-3E54-4876-BC9E-DFEE06CF84CB}" name="Francia" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{DFC70003-9000-4DA5-BE54-A5C4C47C974F}" name="Germania" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{D612C1CB-7AAE-4AB2-8068-8FD6B4EC51E1}" name="Spagna" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{57F8BC07-5C6C-4408-9160-2F0D9F6AFA18}" name="Snack" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{26F26539-D5D0-47BE-A212-86FC4674E49D}" name="Italia" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{F6304A94-3E54-4876-BC9E-DFEE06CF84CB}" name="Francia" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{DFC70003-9000-4DA5-BE54-A5C4C47C974F}" name="Germania" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{D612C1CB-7AAE-4AB2-8068-8FD6B4EC51E1}" name="Spagna" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8058,10 +8146,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
@@ -8090,65 +8178,65 @@
       <c r="X1" s="1"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="7">
         <v>70</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="7">
         <v>42</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>35</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>23</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>80</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>55</v>
       </c>
     </row>
@@ -8177,11 +8265,11 @@
     <col min="8" max="8" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:25" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="1"/>
@@ -8209,249 +8297,249 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="15">
         <v>70.5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <v>71</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="11"/>
     </row>
     <row r="4" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <v>70.5</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <v>71</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <v>71.5</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="11"/>
     </row>
     <row r="7" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <v>71.5</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>8</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>9</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <v>71.5</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>10</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>11</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="15">
         <v>72.400000000000006</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>12</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <v>72.900000000000006</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="15">
         <v>72.400000000000006</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>14</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="15">
         <v>72.900000000000006</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>15</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <v>73.400000000000006</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>16</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <v>72.900000000000006</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>17</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="15">
         <v>73.400000000000006</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <v>73.900000000000006</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>19</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <v>73.400000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>20</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <v>73.900000000000006</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>21</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="15">
         <v>74.400000000000006</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>22</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <v>73.900000000000006</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>23</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="15">
         <v>74.400000000000006</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>24</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="15">
         <v>74.900000000000006</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>25</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="15">
         <v>74.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>26</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="15">
         <v>74.900000000000006</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>27</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="15">
         <v>75.400000000000006</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>28</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="15">
         <v>74.900000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>29</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="15">
         <v>75.400000000000006</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
+      <c r="A31" s="16">
         <v>30</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="17">
         <v>75.900000000000006</v>
       </c>
     </row>
@@ -8480,10 +8568,10 @@
     <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="10.44140625" customWidth="1"/>
     <col min="12" max="12" width="20.77734375" customWidth="1"/>
-    <col min="13" max="13" width="35.5546875" customWidth="1"/>
+    <col min="13" max="13" width="39.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -8528,7 +8616,7 @@
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -8549,11 +8637,11 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -8574,9 +8662,9 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="M3" s="5"/>
+      <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -8597,9 +8685,9 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="M4" s="5"/>
+      <c r="M4" s="9"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
@@ -8620,9 +8708,9 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="9"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -8643,9 +8731,9 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="9"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
@@ -8666,9 +8754,9 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="9"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -8689,9 +8777,9 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="9"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -8712,9 +8800,9 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="9"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -8735,9 +8823,9 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="M10" s="15"/>
+      <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
@@ -8758,16 +8846,16 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="M11" s="15"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M12" s="15"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M13" s="15"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M14" s="15"/>
+      <c r="M14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
